--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/13.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/13.xlsx
@@ -426,13 +426,13 @@
         <v>-15.19738571481996</v>
       </c>
       <c r="E2">
-        <v>-16.40059977980104</v>
+        <v>-22.90673084220516</v>
       </c>
       <c r="F2">
-        <v>-2.990360911146569</v>
+        <v>-3.993370528376086</v>
       </c>
       <c r="G2">
-        <v>-11.20768378012003</v>
+        <v>-14.79732211943397</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.09014001831425</v>
       </c>
       <c r="E3">
-        <v>-16.84228902061317</v>
+        <v>-23.98049542805991</v>
       </c>
       <c r="F3">
-        <v>-3.232031302341505</v>
+        <v>-4.135152236304444</v>
       </c>
       <c r="G3">
-        <v>-11.28175735682449</v>
+        <v>-14.19886504103919</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.01806431655677</v>
       </c>
       <c r="E4">
-        <v>-17.21473789384803</v>
+        <v>-24.27783050292954</v>
       </c>
       <c r="F4">
-        <v>-3.129944131987897</v>
+        <v>-3.913369289715918</v>
       </c>
       <c r="G4">
-        <v>-10.70062676887436</v>
+        <v>-15.42284435386183</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.97216499971596</v>
       </c>
       <c r="E5">
-        <v>-18.02398525596674</v>
+        <v>-23.99310722817127</v>
       </c>
       <c r="F5">
-        <v>-3.279191915317687</v>
+        <v>-3.933545006178503</v>
       </c>
       <c r="G5">
-        <v>-10.4368329616028</v>
+        <v>-14.85419881394539</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.95447135731401</v>
       </c>
       <c r="E6">
-        <v>-18.60023357344279</v>
+        <v>-25.12606349778028</v>
       </c>
       <c r="F6">
-        <v>-3.102719008927489</v>
+        <v>-3.924473554750445</v>
       </c>
       <c r="G6">
-        <v>-10.2875505055343</v>
+        <v>-14.67856322692221</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.97452326547592</v>
       </c>
       <c r="E7">
-        <v>-19.08143827844586</v>
+        <v>-25.48977241618033</v>
       </c>
       <c r="F7">
-        <v>-2.919602595966838</v>
+        <v>-4.143890684036576</v>
       </c>
       <c r="G7">
-        <v>-10.30106913835922</v>
+        <v>-13.79608032912033</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.00698258077868</v>
       </c>
       <c r="E8">
-        <v>-19.13870083227285</v>
+        <v>-26.13044733336351</v>
       </c>
       <c r="F8">
-        <v>-2.743194302234058</v>
+        <v>-3.774833125271729</v>
       </c>
       <c r="G8">
-        <v>-9.829761036003696</v>
+        <v>-14.06616587873213</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.06822775910551</v>
       </c>
       <c r="E9">
-        <v>-19.76089051855672</v>
+        <v>-26.18096246091908</v>
       </c>
       <c r="F9">
-        <v>-2.761224547123392</v>
+        <v>-3.669197228964527</v>
       </c>
       <c r="G9">
-        <v>-10.11378029296767</v>
+        <v>-13.9177759149278</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.13222568278735</v>
       </c>
       <c r="E10">
-        <v>-20.96220410331151</v>
+        <v>-26.48682012387114</v>
       </c>
       <c r="F10">
-        <v>-2.349205369747155</v>
+        <v>-3.830214456353293</v>
       </c>
       <c r="G10">
-        <v>-9.881056372642496</v>
+        <v>-13.83935964148941</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.19337809155154</v>
       </c>
       <c r="E11">
-        <v>-21.0713040991043</v>
+        <v>-27.22272884943563</v>
       </c>
       <c r="F11">
-        <v>-2.496899964196695</v>
+        <v>-3.24890183286692</v>
       </c>
       <c r="G11">
-        <v>-9.705832578925028</v>
+        <v>-14.00491039404963</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.24573324178542</v>
       </c>
       <c r="E12">
-        <v>-21.71105520758992</v>
+        <v>-27.40941971887585</v>
       </c>
       <c r="F12">
-        <v>-2.473434800777594</v>
+        <v>-3.708207535064564</v>
       </c>
       <c r="G12">
-        <v>-9.229829048517942</v>
+        <v>-13.96920906287209</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.25788701827241</v>
       </c>
       <c r="E13">
-        <v>-20.93315847102631</v>
+        <v>-27.56581056873074</v>
       </c>
       <c r="F13">
-        <v>-2.413843706555003</v>
+        <v>-2.968990688889147</v>
       </c>
       <c r="G13">
-        <v>-8.894307737956924</v>
+        <v>-12.97312863407146</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.2379350183929</v>
       </c>
       <c r="E14">
-        <v>-22.89757426776165</v>
+        <v>-28.27870106091424</v>
       </c>
       <c r="F14">
-        <v>-2.1348114603916</v>
+        <v>-3.041014749460356</v>
       </c>
       <c r="G14">
-        <v>-8.384924340625608</v>
+        <v>-12.55264665367174</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.15509134281003</v>
       </c>
       <c r="E15">
-        <v>-23.17937214831096</v>
+        <v>-29.62863916260077</v>
       </c>
       <c r="F15">
-        <v>-1.769600839845354</v>
+        <v>-2.936197280147121</v>
       </c>
       <c r="G15">
-        <v>-8.00447654447267</v>
+        <v>-12.90748123433165</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.00598009559175</v>
       </c>
       <c r="E16">
-        <v>-24.43950608195139</v>
+        <v>-30.5510168623791</v>
       </c>
       <c r="F16">
-        <v>-1.901789224881891</v>
+        <v>-2.903811428167271</v>
       </c>
       <c r="G16">
-        <v>-7.666199007801717</v>
+        <v>-12.54006316899127</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.78449284239103</v>
       </c>
       <c r="E17">
-        <v>-25.02102101469836</v>
+        <v>-30.7982104087988</v>
       </c>
       <c r="F17">
-        <v>-1.745020693902085</v>
+        <v>-2.765430168427405</v>
       </c>
       <c r="G17">
-        <v>-7.538526676923723</v>
+        <v>-12.57806955831432</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.47361989743432</v>
       </c>
       <c r="E18">
-        <v>-25.55045396788312</v>
+        <v>-31.47711470355473</v>
       </c>
       <c r="F18">
-        <v>-1.406514153319886</v>
+        <v>-2.627235291353169</v>
       </c>
       <c r="G18">
-        <v>-6.863225030217525</v>
+        <v>-12.21333553220956</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.09061756023943</v>
       </c>
       <c r="E19">
-        <v>-25.99604222481586</v>
+        <v>-31.42550368528931</v>
       </c>
       <c r="F19">
-        <v>-1.355428735589241</v>
+        <v>-2.44674977326381</v>
       </c>
       <c r="G19">
-        <v>-6.674062607315538</v>
+        <v>-11.89645156010619</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.62145115026515</v>
       </c>
       <c r="E20">
-        <v>-26.51113350081832</v>
+        <v>-32.08559896325438</v>
       </c>
       <c r="F20">
-        <v>-1.012443212460105</v>
+        <v>-2.026361600017089</v>
       </c>
       <c r="G20">
-        <v>-6.600454964072514</v>
+        <v>-11.1783332532708</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.08192233056393</v>
       </c>
       <c r="E21">
-        <v>-27.17747580867698</v>
+        <v>-33.3684590437023</v>
       </c>
       <c r="F21">
-        <v>-0.7536015933725384</v>
+        <v>-2.051373325377218</v>
       </c>
       <c r="G21">
-        <v>-6.395834706403982</v>
+        <v>-10.91395866978322</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.47995962440223</v>
       </c>
       <c r="E22">
-        <v>-28.03254227080529</v>
+        <v>-33.17678232437964</v>
       </c>
       <c r="F22">
-        <v>-0.595494420669808</v>
+        <v>-1.995716976317924</v>
       </c>
       <c r="G22">
-        <v>-6.380517964164494</v>
+        <v>-10.13389418112707</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.82139543892129</v>
       </c>
       <c r="E23">
-        <v>-27.99933949938105</v>
+        <v>-34.15637276477087</v>
       </c>
       <c r="F23">
-        <v>-0.6133548502415681</v>
+        <v>-1.384250951002247</v>
       </c>
       <c r="G23">
-        <v>-5.959547081752416</v>
+        <v>-10.351038861488</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.14245512224965</v>
       </c>
       <c r="E24">
-        <v>-29.14942698616108</v>
+        <v>-34.05042232265041</v>
       </c>
       <c r="F24">
-        <v>-0.4944236571194346</v>
+        <v>-1.91025762484071</v>
       </c>
       <c r="G24">
-        <v>-5.588394986277386</v>
+        <v>-10.51624508578448</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.45261827859741</v>
       </c>
       <c r="E25">
-        <v>-29.50055353953082</v>
+        <v>-34.52653249439486</v>
       </c>
       <c r="F25">
-        <v>-0.2876051676624821</v>
+        <v>-1.642502772499021</v>
       </c>
       <c r="G25">
-        <v>-5.731059218460484</v>
+        <v>-10.7211737782796</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.791879481896448</v>
       </c>
       <c r="E26">
-        <v>-29.08323881006497</v>
+        <v>-34.81237430223302</v>
       </c>
       <c r="F26">
-        <v>-0.1370551907754916</v>
+        <v>-1.534558216240217</v>
       </c>
       <c r="G26">
-        <v>-5.509665356180069</v>
+        <v>-9.826988403785965</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.181026352209422</v>
       </c>
       <c r="E27">
-        <v>-29.49519635477975</v>
+        <v>-34.52989262210855</v>
       </c>
       <c r="F27">
-        <v>-0.4151522101411332</v>
+        <v>-1.116028071077975</v>
       </c>
       <c r="G27">
-        <v>-5.422995169908897</v>
+        <v>-10.62460086534202</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.633878446493476</v>
       </c>
       <c r="E28">
-        <v>-30.16117412048078</v>
+        <v>-35.90043301629297</v>
       </c>
       <c r="F28">
-        <v>-0.3868394406808489</v>
+        <v>-1.068417654602074</v>
       </c>
       <c r="G28">
-        <v>-6.174286626710275</v>
+        <v>-11.54011417997205</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.174164559669665</v>
       </c>
       <c r="E29">
-        <v>-29.95247713160029</v>
+        <v>-35.14956221260714</v>
       </c>
       <c r="F29">
-        <v>-0.195053334482499</v>
+        <v>-1.498433113804131</v>
       </c>
       <c r="G29">
-        <v>-5.982778130393284</v>
+        <v>-10.3270662567747</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.789727711490045</v>
       </c>
       <c r="E30">
-        <v>-30.08091823987985</v>
+        <v>-35.52419154607669</v>
       </c>
       <c r="F30">
-        <v>-0.4269779831834989</v>
+        <v>-1.591547408450615</v>
       </c>
       <c r="G30">
-        <v>-6.169692916527053</v>
+        <v>-10.67640479132254</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.489725760400622</v>
       </c>
       <c r="E31">
-        <v>-29.80761577656892</v>
+        <v>-35.68527163076654</v>
       </c>
       <c r="F31">
-        <v>-0.3727282019741593</v>
+        <v>-1.324532288199625</v>
       </c>
       <c r="G31">
-        <v>-6.471227334175344</v>
+        <v>-11.45850363734554</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.257961270772051</v>
       </c>
       <c r="E32">
-        <v>-28.60978685256303</v>
+        <v>-34.58997415100531</v>
       </c>
       <c r="F32">
-        <v>-0.3125912136331236</v>
+        <v>-1.116725556431132</v>
       </c>
       <c r="G32">
-        <v>-6.068276920567736</v>
+        <v>-11.08638358151048</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.078278749102052</v>
       </c>
       <c r="E33">
-        <v>-29.54303741843378</v>
+        <v>-35.97638231811262</v>
       </c>
       <c r="F33">
-        <v>-0.2974088958746143</v>
+        <v>-1.450637971397405</v>
       </c>
       <c r="G33">
-        <v>-6.620913380495653</v>
+        <v>-11.59132092362874</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.943355216151637</v>
       </c>
       <c r="E34">
-        <v>-29.01822803721085</v>
+        <v>-33.28657517669561</v>
       </c>
       <c r="F34">
-        <v>-0.2406160267386802</v>
+        <v>-1.36835043870551</v>
       </c>
       <c r="G34">
-        <v>-6.188625564925049</v>
+        <v>-10.72299157502353</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.824962118252444</v>
       </c>
       <c r="E35">
-        <v>-28.67816228160485</v>
+        <v>-34.03837658179001</v>
       </c>
       <c r="F35">
-        <v>-0.3364564785077773</v>
+        <v>-1.926974079029204</v>
       </c>
       <c r="G35">
-        <v>-6.756076740193858</v>
+        <v>-11.22500206751078</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.718891170546365</v>
       </c>
       <c r="E36">
-        <v>-28.89481353507981</v>
+        <v>-33.07295573656878</v>
       </c>
       <c r="F36">
-        <v>-0.1141665710687384</v>
+        <v>-1.366661397571202</v>
       </c>
       <c r="G36">
-        <v>-6.940146707235588</v>
+        <v>-10.75122648654255</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.604321708286861</v>
       </c>
       <c r="E37">
-        <v>-28.27642776696239</v>
+        <v>-33.36184067894009</v>
       </c>
       <c r="F37">
-        <v>-0.1484858325667219</v>
+        <v>-1.282381641275575</v>
       </c>
       <c r="G37">
-        <v>-6.516787095528234</v>
+        <v>-11.95271466618599</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.46954180739785</v>
       </c>
       <c r="E38">
-        <v>-28.58829924339664</v>
+        <v>-32.74319225933022</v>
       </c>
       <c r="F38">
-        <v>-0.1556362999876873</v>
+        <v>-1.866530594749133</v>
       </c>
       <c r="G38">
-        <v>-6.573676914925886</v>
+        <v>-11.51929482917737</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.310734566184768</v>
       </c>
       <c r="E39">
-        <v>-27.10207218797526</v>
+        <v>-32.13838059205079</v>
       </c>
       <c r="F39">
-        <v>-0.3022796962030753</v>
+        <v>-1.684844772293117</v>
       </c>
       <c r="G39">
-        <v>-6.861535201114411</v>
+        <v>-11.01295968667478</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.114100493830952</v>
       </c>
       <c r="E40">
-        <v>-26.90853426583544</v>
+        <v>-32.43970525252117</v>
       </c>
       <c r="F40">
-        <v>-0.1618863320418095</v>
+        <v>-1.391238230044861</v>
       </c>
       <c r="G40">
-        <v>-6.933925511158881</v>
+        <v>-11.89208425421057</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.890067306055816</v>
       </c>
       <c r="E41">
-        <v>-25.81949060867881</v>
+        <v>-31.19912526964587</v>
       </c>
       <c r="F41">
-        <v>-0.02709687336048238</v>
+        <v>-1.480473280144035</v>
       </c>
       <c r="G41">
-        <v>-6.291222800645766</v>
+        <v>-11.95502136494228</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.638802459982753</v>
       </c>
       <c r="E42">
-        <v>-26.23880918789306</v>
+        <v>-31.80126966573479</v>
       </c>
       <c r="F42">
-        <v>-0.1960622859791087</v>
+        <v>-1.36379938819453</v>
       </c>
       <c r="G42">
-        <v>-6.619758390506727</v>
+        <v>-11.09533147270308</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.374319681184019</v>
       </c>
       <c r="E43">
-        <v>-25.29869798390069</v>
+        <v>-31.25238238821308</v>
       </c>
       <c r="F43">
-        <v>-0.3309552905857858</v>
+        <v>-1.661595812766147</v>
       </c>
       <c r="G43">
-        <v>-6.280762266314256</v>
+        <v>-11.71219784465713</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.11605213457721</v>
       </c>
       <c r="E44">
-        <v>-24.12916522973173</v>
+        <v>-31.09739989377457</v>
       </c>
       <c r="F44">
-        <v>-0.1561979330867853</v>
+        <v>-1.477857295885994</v>
       </c>
       <c r="G44">
-        <v>-6.093850761402048</v>
+        <v>-11.71676202384632</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.873743593801665</v>
       </c>
       <c r="E45">
-        <v>-24.58637355096815</v>
+        <v>-31.00922371213422</v>
       </c>
       <c r="F45">
-        <v>-0.2183122344183035</v>
+        <v>-1.401258990516526</v>
       </c>
       <c r="G45">
-        <v>-6.470889368354721</v>
+        <v>-11.33075583837168</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.675778769870164</v>
       </c>
       <c r="E46">
-        <v>-24.12734931165465</v>
+        <v>-29.12070287553043</v>
       </c>
       <c r="F46">
-        <v>-0.107793112271599</v>
+        <v>-1.387501464690832</v>
       </c>
       <c r="G46">
-        <v>-6.147288735719164</v>
+        <v>-11.18718270781662</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.530937107870973</v>
       </c>
       <c r="E47">
-        <v>-23.86515519508455</v>
+        <v>-30.34594718117875</v>
       </c>
       <c r="F47">
-        <v>-0.1855246242480962</v>
+        <v>-1.689360203005777</v>
       </c>
       <c r="G47">
-        <v>-6.708410434599805</v>
+        <v>-11.18072526378763</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.456461050686551</v>
       </c>
       <c r="E48">
-        <v>-22.94193519914079</v>
+        <v>-28.88771741630979</v>
       </c>
       <c r="F48">
-        <v>-0.1475870539346845</v>
+        <v>-1.379849834991173</v>
       </c>
       <c r="G48">
-        <v>-6.629641429843775</v>
+        <v>-11.19322671792911</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.462702196419461</v>
       </c>
       <c r="E49">
-        <v>-22.5064726100892</v>
+        <v>-29.00578831911178</v>
       </c>
       <c r="F49">
-        <v>-0.1533839690194754</v>
+        <v>-1.50811755711026</v>
       </c>
       <c r="G49">
-        <v>-6.377407366126141</v>
+        <v>-10.59155568301686</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.544786486350452</v>
       </c>
       <c r="E50">
-        <v>-21.95007712266278</v>
+        <v>-27.5785989793284</v>
       </c>
       <c r="F50">
-        <v>0.02595011837999236</v>
+        <v>-1.505696239191877</v>
       </c>
       <c r="G50">
-        <v>-6.070219403730927</v>
+        <v>-11.5279014733278</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.710976826108327</v>
       </c>
       <c r="E51">
-        <v>-22.12949073437267</v>
+        <v>-27.50419615138238</v>
       </c>
       <c r="F51">
-        <v>-0.08909851672521978</v>
+        <v>-1.235761123846019</v>
       </c>
       <c r="G51">
-        <v>-6.640909144678909</v>
+        <v>-11.76041539547317</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.944934823254695</v>
       </c>
       <c r="E52">
-        <v>-20.88990248730504</v>
+        <v>-28.16076601233248</v>
       </c>
       <c r="F52">
-        <v>0.03242960820469009</v>
+        <v>-1.649946481980577</v>
       </c>
       <c r="G52">
-        <v>-6.35011416519468</v>
+        <v>-11.48787385152413</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.242587811528731</v>
       </c>
       <c r="E53">
-        <v>-20.98966024122002</v>
+        <v>-27.51452107211987</v>
       </c>
       <c r="F53">
-        <v>0.1113721933240802</v>
+        <v>-1.653561477326394</v>
       </c>
       <c r="G53">
-        <v>-6.091009223531569</v>
+        <v>-10.99301314081492</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.591033561057169</v>
       </c>
       <c r="E54">
-        <v>-19.86080676906196</v>
+        <v>-25.40558808437774</v>
       </c>
       <c r="F54">
-        <v>0.01189106681967915</v>
+        <v>-1.535507525283825</v>
       </c>
       <c r="G54">
-        <v>-6.852252625322743</v>
+        <v>-11.504260271992</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.970005235799451</v>
       </c>
       <c r="E55">
-        <v>-20.23455531433702</v>
+        <v>-27.62298708155159</v>
       </c>
       <c r="F55">
-        <v>-0.158170275872851</v>
+        <v>-1.371011154803302</v>
       </c>
       <c r="G55">
-        <v>-7.508362407127748</v>
+        <v>-11.11702362843257</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.375209361624467</v>
       </c>
       <c r="E56">
-        <v>-19.801796224268</v>
+        <v>-25.48628096272042</v>
       </c>
       <c r="F56">
-        <v>-0.2255836434800775</v>
+        <v>-1.276772765591219</v>
       </c>
       <c r="G56">
-        <v>-7.040135371816547</v>
+        <v>-10.49008390629103</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.782700838506657</v>
       </c>
       <c r="E57">
-        <v>-19.1817077499237</v>
+        <v>-26.33465886873941</v>
       </c>
       <c r="F57">
-        <v>-0.02759140869995369</v>
+        <v>-1.183786039524766</v>
       </c>
       <c r="G57">
-        <v>-6.784718523186251</v>
+        <v>-11.03471090439234</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.189897511910696</v>
       </c>
       <c r="E58">
-        <v>-17.93337049107325</v>
+        <v>-25.55047208177915</v>
       </c>
       <c r="F58">
-        <v>0.0521820289244443</v>
+        <v>-1.460429274098495</v>
       </c>
       <c r="G58">
-        <v>-6.799457770431277</v>
+        <v>-11.93589512447227</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.58588068033775</v>
       </c>
       <c r="E59">
-        <v>-18.52454013040458</v>
+        <v>-24.93892883788731</v>
       </c>
       <c r="F59">
-        <v>-0.2559308832816374</v>
+        <v>-0.962679869104328</v>
       </c>
       <c r="G59">
-        <v>-7.110579917476265</v>
+        <v>-12.05127599938859</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.959714938972874</v>
       </c>
       <c r="E60">
-        <v>-18.34389024529059</v>
+        <v>-23.87990443492753</v>
       </c>
       <c r="F60">
-        <v>-0.2886141191590919</v>
+        <v>-1.458765912353674</v>
       </c>
       <c r="G60">
-        <v>-7.912736870892155</v>
+        <v>-11.68256841397534</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.315946203367957</v>
       </c>
       <c r="E61">
-        <v>-17.64793624589578</v>
+        <v>-25.274081199195</v>
       </c>
       <c r="F61">
-        <v>-0.3290525306615554</v>
+        <v>-1.676855997060519</v>
       </c>
       <c r="G61">
-        <v>-7.668863359707987</v>
+        <v>-11.91189298876493</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.639890904065483</v>
       </c>
       <c r="E62">
-        <v>-17.4184648825051</v>
+        <v>-24.68715474000885</v>
       </c>
       <c r="F62">
-        <v>-0.3223734042927829</v>
+        <v>-1.304166875601799</v>
       </c>
       <c r="G62">
-        <v>-7.913553895060457</v>
+        <v>-11.84874259863186</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.941144993615557</v>
       </c>
       <c r="E63">
-        <v>-17.79805063077605</v>
+        <v>-23.90091202584911</v>
       </c>
       <c r="F63">
-        <v>-0.2242367180831255</v>
+        <v>-1.479089906581359</v>
       </c>
       <c r="G63">
-        <v>-8.372741164975389</v>
+        <v>-12.40320669896839</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.215619774699052</v>
       </c>
       <c r="E64">
-        <v>-17.01020030834358</v>
+        <v>-23.35775779642112</v>
       </c>
       <c r="F64">
-        <v>-0.2738923736765391</v>
+        <v>-1.679901904000613</v>
       </c>
       <c r="G64">
-        <v>-7.883865402390602</v>
+        <v>-12.2100313420992</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.461101266278774</v>
       </c>
       <c r="E65">
-        <v>-17.05875913512783</v>
+        <v>-23.9672677554835</v>
       </c>
       <c r="F65">
-        <v>-0.1175877284423004</v>
+        <v>-1.503961637850415</v>
       </c>
       <c r="G65">
-        <v>-8.338652554194317</v>
+        <v>-13.2286636066779</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.686073150407452</v>
       </c>
       <c r="E66">
-        <v>-17.37734633851545</v>
+        <v>-23.83368682920525</v>
       </c>
       <c r="F66">
-        <v>-0.1639738178968643</v>
+        <v>-1.669412287578963</v>
       </c>
       <c r="G66">
-        <v>-8.303379422430288</v>
+        <v>-13.43420588760463</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.877628168803712</v>
       </c>
       <c r="E67">
-        <v>-16.7627826024605</v>
+        <v>-23.86125617896394</v>
       </c>
       <c r="F67">
-        <v>-0.5314160602262522</v>
+        <v>-2.143401630358631</v>
       </c>
       <c r="G67">
-        <v>-8.65997273784606</v>
+        <v>-14.36115918120166</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.04739834132169</v>
       </c>
       <c r="E68">
-        <v>-16.36059524041728</v>
+        <v>-23.32020768994951</v>
       </c>
       <c r="F68">
-        <v>-0.6312716087967186</v>
+        <v>-1.924439274776638</v>
       </c>
       <c r="G68">
-        <v>-8.674672610432372</v>
+        <v>-13.42129428076822</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.18826863315617</v>
       </c>
       <c r="E69">
-        <v>-16.20467535185918</v>
+        <v>-23.00652029543819</v>
       </c>
       <c r="F69">
-        <v>-0.7272901595574177</v>
+        <v>-1.992502910795062</v>
       </c>
       <c r="G69">
-        <v>-8.603660413442871</v>
+        <v>-12.61598079221214</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.29884879960789</v>
       </c>
       <c r="E70">
-        <v>-15.35875187875235</v>
+        <v>-22.26920321445731</v>
       </c>
       <c r="F70">
-        <v>-0.5666398989280927</v>
+        <v>-2.218460829093697</v>
       </c>
       <c r="G70">
-        <v>-8.48222896597094</v>
+        <v>-13.23952773126122</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.38547453787832</v>
       </c>
       <c r="E71">
-        <v>-17.09494164244912</v>
+        <v>-21.95814686334445</v>
       </c>
       <c r="F71">
-        <v>-0.8381016953973104</v>
+        <v>-1.890355269621049</v>
       </c>
       <c r="G71">
-        <v>-9.01245140142629</v>
+        <v>-12.83462499082574</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.43470597105759</v>
       </c>
       <c r="E72">
-        <v>-15.75665077591031</v>
+        <v>-21.84684602918392</v>
       </c>
       <c r="F72">
-        <v>-0.9921871443594492</v>
+        <v>-2.052240626047948</v>
       </c>
       <c r="G72">
-        <v>-8.506211414348922</v>
+        <v>-13.40795611512907</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.45996432712388</v>
       </c>
       <c r="E73">
-        <v>-16.17159937770715</v>
+        <v>-22.71534394521899</v>
       </c>
       <c r="F73">
-        <v>-0.804323357813355</v>
+        <v>-2.069874082951342</v>
       </c>
       <c r="G73">
-        <v>-8.630123465319791</v>
+        <v>-12.38544872788867</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.45319658902396</v>
       </c>
       <c r="E74">
-        <v>-16.84476156742136</v>
+        <v>-23.48403882259901</v>
       </c>
       <c r="F74">
-        <v>-1.069606361825091</v>
+        <v>-2.319900216138316</v>
       </c>
       <c r="G74">
-        <v>-8.311694037861919</v>
+        <v>-12.80359775975963</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.41716909388912</v>
       </c>
       <c r="E75">
-        <v>-17.14977240573399</v>
+        <v>-23.35424370059116</v>
       </c>
       <c r="F75">
-        <v>-1.164826366409491</v>
+        <v>-2.116331412002546</v>
       </c>
       <c r="G75">
-        <v>-8.881202539048502</v>
+        <v>-13.22469332859097</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.35772427382433</v>
       </c>
       <c r="E76">
-        <v>-16.92007914711693</v>
+        <v>-23.44517998713919</v>
       </c>
       <c r="F76">
-        <v>-1.265776188319056</v>
+        <v>-2.880897957438434</v>
       </c>
       <c r="G76">
-        <v>-7.950575917915672</v>
+        <v>-12.11620809282844</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.26262385523001</v>
       </c>
       <c r="E77">
-        <v>-16.9788043980484</v>
+        <v>-24.92450564817288</v>
       </c>
       <c r="F77">
-        <v>-1.362471515247842</v>
+        <v>-2.282358605443443</v>
       </c>
       <c r="G77">
-        <v>-7.660968740635963</v>
+        <v>-12.03540801192711</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.14619132200911</v>
       </c>
       <c r="E78">
-        <v>-17.65088881094878</v>
+        <v>-23.10534065523357</v>
       </c>
       <c r="F78">
-        <v>-1.305786333874272</v>
+        <v>-2.743395595512939</v>
       </c>
       <c r="G78">
-        <v>-8.018247831357661</v>
+        <v>-12.57197961109999</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.998502206443664</v>
       </c>
       <c r="E79">
-        <v>-17.42225974372353</v>
+        <v>-24.59398591577504</v>
       </c>
       <c r="F79">
-        <v>-1.29811896519396</v>
+        <v>-2.523774687845719</v>
       </c>
       <c r="G79">
-        <v>-8.004332170724055</v>
+        <v>-12.35126496168238</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.824401465912857</v>
       </c>
       <c r="E80">
-        <v>-18.23115841334365</v>
+        <v>-25.4253412879992</v>
       </c>
       <c r="F80">
-        <v>-1.507063873773899</v>
+        <v>-3.002642286260475</v>
       </c>
       <c r="G80">
-        <v>-7.390628896353313</v>
+        <v>-12.04906773727908</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.627781723719526</v>
       </c>
       <c r="E81">
-        <v>-18.655263589584</v>
+        <v>-25.00046627117754</v>
       </c>
       <c r="F81">
-        <v>-1.47042021334366</v>
+        <v>-2.668147529010034</v>
       </c>
       <c r="G81">
-        <v>-7.47089413814045</v>
+        <v>-11.87626876629404</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.398892756963154</v>
       </c>
       <c r="E82">
-        <v>-19.50862734548543</v>
+        <v>-25.75218842797682</v>
       </c>
       <c r="F82">
-        <v>-1.459659720781294</v>
+        <v>-2.764255543450235</v>
       </c>
       <c r="G82">
-        <v>-7.012120302142008</v>
+        <v>-10.97747655673095</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.152878659330504</v>
       </c>
       <c r="E83">
-        <v>-20.50696566826842</v>
+        <v>-25.77620292563949</v>
       </c>
       <c r="F83">
-        <v>-1.402761648985205</v>
+        <v>-3.061462170431059</v>
       </c>
       <c r="G83">
-        <v>-6.755975022325516</v>
+        <v>-11.17129503302579</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.880895991309428</v>
       </c>
       <c r="E84">
-        <v>-21.55033060810968</v>
+        <v>-26.87052678348907</v>
       </c>
       <c r="F84">
-        <v>-1.723623963887774</v>
+        <v>-2.238612522901601</v>
       </c>
       <c r="G84">
-        <v>-6.791720649994106</v>
+        <v>-11.69541439638057</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.592363082314384</v>
       </c>
       <c r="E85">
-        <v>-22.44065124038771</v>
+        <v>-27.69468188204102</v>
       </c>
       <c r="F85">
-        <v>-1.651319086767016</v>
+        <v>-3.083913412149134</v>
       </c>
       <c r="G85">
-        <v>-6.253980935946069</v>
+        <v>-10.64959721118187</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.291996812285054</v>
       </c>
       <c r="E86">
-        <v>-23.07202920043315</v>
+        <v>-28.8286208305097</v>
       </c>
       <c r="F86">
-        <v>-1.515125545337944</v>
+        <v>-3.118158948948268</v>
       </c>
       <c r="G86">
-        <v>-6.359951267429895</v>
+        <v>-10.36219173356855</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.977125376716092</v>
       </c>
       <c r="E87">
-        <v>-24.06711607887863</v>
+        <v>-29.71080832346995</v>
       </c>
       <c r="F87">
-        <v>-1.675412152677439</v>
+        <v>-2.938406536010387</v>
       </c>
       <c r="G87">
-        <v>-5.621269545081463</v>
+        <v>-11.07363931697359</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.667476682922998</v>
       </c>
       <c r="E88">
-        <v>-25.59038605168275</v>
+        <v>-30.36291084481148</v>
       </c>
       <c r="F88">
-        <v>-1.917083372239778</v>
+        <v>-3.094831294518031</v>
       </c>
       <c r="G88">
-        <v>-5.592539169106965</v>
+        <v>-11.16038497134063</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.360177453277384</v>
       </c>
       <c r="E89">
-        <v>-26.99440318996889</v>
+        <v>-32.57318655237126</v>
       </c>
       <c r="F89">
-        <v>-1.875399924530907</v>
+        <v>-3.152522942286003</v>
       </c>
       <c r="G89">
-        <v>-6.214078000561662</v>
+        <v>-9.708204902112508</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.07499227885921</v>
       </c>
       <c r="E90">
-        <v>-28.68775358955309</v>
+        <v>-32.76350925796564</v>
       </c>
       <c r="F90">
-        <v>-1.813033799508938</v>
+        <v>-3.188965309437362</v>
       </c>
       <c r="G90">
-        <v>-5.104523086570753</v>
+        <v>-10.87169325487601</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.823035565419509</v>
       </c>
       <c r="E91">
-        <v>-29.96369642595429</v>
+        <v>-34.9479794563927</v>
       </c>
       <c r="F91">
-        <v>-1.950570952865351</v>
+        <v>-3.619202771103369</v>
       </c>
       <c r="G91">
-        <v>-5.24919542634823</v>
+        <v>-9.964310807270286</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.611425333849925</v>
       </c>
       <c r="E92">
-        <v>-30.96480617482998</v>
+        <v>-36.62134796441806</v>
       </c>
       <c r="F92">
-        <v>-2.31800739662292</v>
+        <v>-3.376887081701652</v>
       </c>
       <c r="G92">
-        <v>-5.425150932473453</v>
+        <v>-9.590537015769261</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.463459347676185</v>
       </c>
       <c r="E93">
-        <v>-32.82007442679544</v>
+        <v>-37.14298741383562</v>
       </c>
       <c r="F93">
-        <v>-2.344784372918414</v>
+        <v>-3.977336648927499</v>
       </c>
       <c r="G93">
-        <v>-5.415546796968957</v>
+        <v>-10.55575427458175</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.375788665641055</v>
       </c>
       <c r="E94">
-        <v>-34.30621091273667</v>
+        <v>-39.21778023603392</v>
       </c>
       <c r="F94">
-        <v>-2.382054279105169</v>
+        <v>-3.928538353595983</v>
       </c>
       <c r="G94">
-        <v>-5.309025220263145</v>
+        <v>-10.21903203692998</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.364920144360272</v>
       </c>
       <c r="E95">
-        <v>-36.1245562518806</v>
+        <v>-40.46545860191625</v>
       </c>
       <c r="F95">
-        <v>-2.484503446013801</v>
+        <v>-3.651717848398055</v>
       </c>
       <c r="G95">
-        <v>-6.239369656341862</v>
+        <v>-11.19124486010721</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.432990863264392</v>
       </c>
       <c r="E96">
-        <v>-38.06661950091407</v>
+        <v>-42.78565848753821</v>
       </c>
       <c r="F96">
-        <v>-2.75991904009658</v>
+        <v>-3.964986519319161</v>
       </c>
       <c r="G96">
-        <v>-5.781672061014918</v>
+        <v>-11.16673413505816</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.569139505865659</v>
       </c>
       <c r="E97">
-        <v>-40.88156649305905</v>
+        <v>-44.52485289373907</v>
       </c>
       <c r="F97">
-        <v>-2.666098976422911</v>
+        <v>-4.109479473756881</v>
       </c>
       <c r="G97">
-        <v>-6.622983831299662</v>
+        <v>-10.80614429178298</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.785747540062013</v>
       </c>
       <c r="E98">
-        <v>-42.67555769898972</v>
+        <v>-46.57681088575369</v>
       </c>
       <c r="F98">
-        <v>-2.661779040417311</v>
+        <v>-3.938703249995736</v>
       </c>
       <c r="G98">
-        <v>-6.335493041925794</v>
+        <v>-10.98493477333557</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.045250269290048</v>
       </c>
       <c r="E99">
-        <v>-44.29508265106389</v>
+        <v>-47.03171421372021</v>
       </c>
       <c r="F99">
-        <v>-2.888986965126771</v>
+        <v>-4.8543482707216</v>
       </c>
       <c r="G99">
-        <v>-7.087916520165181</v>
+        <v>-11.27690443013807</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.370912369295612</v>
       </c>
       <c r="E100">
-        <v>-47.00097946063015</v>
+        <v>-49.03510432200256</v>
       </c>
       <c r="F100">
-        <v>-2.976499011028122</v>
+        <v>-4.723761948242077</v>
       </c>
       <c r="G100">
-        <v>-7.296418462938536</v>
+        <v>-11.70132387640913</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.706129862441452</v>
       </c>
       <c r="E101">
-        <v>-48.74002782354426</v>
+        <v>-51.122379882803</v>
       </c>
       <c r="F101">
-        <v>-3.309648499616416</v>
+        <v>-4.462083170799922</v>
       </c>
       <c r="G101">
-        <v>-7.735701842873875</v>
+        <v>-12.04180311274647</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.104822167349099</v>
       </c>
       <c r="E102">
-        <v>-51.09769630310569</v>
+        <v>-52.45126058035387</v>
       </c>
       <c r="F102">
-        <v>-3.594543930256833</v>
+        <v>-5.088603945294078</v>
       </c>
       <c r="G102">
-        <v>-7.673880347472378</v>
+        <v>-12.18269876650903</v>
       </c>
     </row>
   </sheetData>
